--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="66">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -67,6 +70,27 @@
     <t>2026-05-11</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
     <t>B5579XA</t>
   </si>
   <si>
@@ -94,19 +118,82 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>4 Л. ЛЯTHA TEЧHOCT З</t>
-  </si>
-  <si>
-    <t>17:14</t>
-  </si>
-  <si>
-    <t>16:14</t>
-  </si>
-  <si>
-    <t>09:11</t>
-  </si>
-  <si>
-    <t>16:24</t>
+    <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
+  </si>
+  <si>
+    <t>10 Л. ДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>17:13:00</t>
+  </si>
+  <si>
+    <t>16:13:00</t>
+  </si>
+  <si>
+    <t>09:11:00</t>
+  </si>
+  <si>
+    <t>16:23:00</t>
+  </si>
+  <si>
+    <t>09:31:00</t>
+  </si>
+  <si>
+    <t>14:22:00</t>
+  </si>
+  <si>
+    <t>14:13:00</t>
+  </si>
+  <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>11:07:00</t>
+  </si>
+  <si>
+    <t>08:50:00</t>
+  </si>
+  <si>
+    <t>08:52:00</t>
+  </si>
+  <si>
+    <t>3231412032 3231412032</t>
+  </si>
+  <si>
+    <t>3231498386 3231498386</t>
+  </si>
+  <si>
+    <t>3231556015 3231556015</t>
+  </si>
+  <si>
+    <t>3231749617 3231749617</t>
+  </si>
+  <si>
+    <t>3232017188 3232017188</t>
+  </si>
+  <si>
+    <t>3232099547 3232099547</t>
+  </si>
+  <si>
+    <t>3232100501 3232100501</t>
+  </si>
+  <si>
+    <t>3232102140 3232102140</t>
+  </si>
+  <si>
+    <t>3232466250 3232466250</t>
+  </si>
+  <si>
+    <t>3232520447 3232520447</t>
+  </si>
+  <si>
+    <t>3232521301 3232521301</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
@@ -530,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -539,16 +626,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -588,303 +676,737 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1147</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>79.94</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2">
         <v>1.75</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>139.89</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>143.89</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2">
+        <v>23320</v>
+      </c>
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3">
+        <v>69.2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3">
+        <v>1.75</v>
+      </c>
+      <c r="I3" s="1">
+        <v>121.1</v>
+      </c>
+      <c r="J3">
+        <v>1.8</v>
+      </c>
+      <c r="K3" s="1">
+        <v>124.56</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3">
+        <v>28215</v>
+      </c>
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4">
+        <v>9.49</v>
+      </c>
+      <c r="I4" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="J4">
+        <v>9.49</v>
+      </c>
+      <c r="K4" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4">
+        <v>28215</v>
+      </c>
+      <c r="N4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>102332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1147</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>9.49</v>
-      </c>
-      <c r="H3">
-        <v>9.49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>9.49</v>
-      </c>
-      <c r="J3">
-        <v>9.49</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>103032</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>1147</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4">
-        <v>69.2</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="H4">
-        <v>121.1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J4">
-        <v>124.56</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>103032</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1199</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>77.68000000000001</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5">
         <v>1.75</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>135.94</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.8</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>139.82</v>
       </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
+      <c r="L5" t="s">
+        <v>40</v>
       </c>
       <c r="M5">
-        <v>264856</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>12941</v>
+      </c>
+      <c r="N5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1147</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>43.38</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6">
         <v>1.74</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>75.48</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.79</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>77.65000000000001</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6">
+        <v>91139</v>
+      </c>
+      <c r="N6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>58.34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7">
+        <v>1.7</v>
+      </c>
+      <c r="I7" s="1">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="J7">
+        <v>1.75</v>
+      </c>
+      <c r="K7" s="1">
+        <v>102.1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7">
+        <v>13585</v>
+      </c>
+      <c r="N7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>104670</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8">
+        <v>1.7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>139.42</v>
+      </c>
+      <c r="J8">
+        <v>1.75</v>
+      </c>
+      <c r="K8" s="1">
+        <v>143.52</v>
+      </c>
+      <c r="L8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8">
+        <v>29000</v>
+      </c>
+      <c r="N8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9">
+        <v>23.79</v>
+      </c>
+      <c r="I9" s="1">
+        <v>23.79</v>
+      </c>
+      <c r="J9">
+        <v>23.79</v>
+      </c>
+      <c r="K9" s="1">
+        <v>23.79</v>
+      </c>
+      <c r="L9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9">
+        <v>29000</v>
+      </c>
+      <c r="N9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10">
+        <v>42.1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10">
+        <v>1.7</v>
+      </c>
+      <c r="I10" s="1">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.75</v>
+      </c>
+      <c r="K10" s="1">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10">
+        <v>91990</v>
+      </c>
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>39.49</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11">
+        <v>1.67</v>
+      </c>
+      <c r="I11" s="1">
+        <v>65.95</v>
+      </c>
+      <c r="J11">
+        <v>1.72</v>
+      </c>
+      <c r="K11" s="1">
+        <v>67.92</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11">
+        <v>92772</v>
+      </c>
+      <c r="N11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="E12" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="F12">
+        <v>73.84</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12">
+        <v>1.66</v>
+      </c>
+      <c r="I12" s="1">
+        <v>122.57</v>
+      </c>
+      <c r="J12">
+        <v>1.71</v>
+      </c>
+      <c r="K12" s="1">
+        <v>126.27</v>
+      </c>
+      <c r="L12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12">
+        <v>12510</v>
+      </c>
+      <c r="N12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13">
+        <v>9.49</v>
+      </c>
+      <c r="I13" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="J13">
+        <v>9.49</v>
+      </c>
+      <c r="K13" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="L13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13">
+        <v>12510</v>
+      </c>
+      <c r="N13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>80.11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14">
+        <v>1.66</v>
+      </c>
+      <c r="I14" s="1">
+        <v>132.98</v>
+      </c>
+      <c r="J14">
+        <v>1.71</v>
+      </c>
+      <c r="K14" s="1">
+        <v>136.99</v>
+      </c>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14">
+        <v>24163</v>
+      </c>
+      <c r="N14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15">
+        <v>9.49</v>
+      </c>
+      <c r="I15" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="J15">
+        <v>9.49</v>
+      </c>
+      <c r="K15" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15">
+        <v>24163</v>
+      </c>
+      <c r="N15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="6">
+        <v>646.09</v>
+      </c>
+      <c r="C20" s="6">
+        <v>10</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.7089</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1104.08</v>
+      </c>
+      <c r="F20" s="6">
+        <v>1136.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7">
+        <v>9.49</v>
+      </c>
+      <c r="E21" s="6">
+        <v>28.47</v>
+      </c>
+      <c r="F21" s="6">
+        <v>28.47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="6">
-        <v>270.2</v>
-      </c>
-      <c r="C11" s="6">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.7484</v>
-      </c>
-      <c r="E11" s="6">
-        <v>472.41</v>
-      </c>
-      <c r="F11" s="6">
-        <v>485.92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="6">
+      <c r="B22" s="6">
         <v>1</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D12" s="7">
-        <v>9.49</v>
-      </c>
-      <c r="E12" s="6">
-        <v>9.49</v>
-      </c>
-      <c r="F12" s="6">
-        <v>9.49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="9">
-        <v>271.2</v>
-      </c>
-      <c r="C13" s="9">
-        <v>5</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>481.9</v>
-      </c>
-      <c r="F13" s="9">
-        <v>495.41</v>
+      <c r="D22" s="7">
+        <v>23.79</v>
+      </c>
+      <c r="E22" s="6">
+        <v>23.79</v>
+      </c>
+      <c r="F22" s="6">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="9">
+        <v>650.09</v>
+      </c>
+      <c r="C23" s="9">
+        <v>14</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="9">
+        <v>1156.34</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1188.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -247,7 +247,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,12 +257,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -312,17 +306,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="82">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-02</t>
   </si>
   <si>
@@ -73,16 +82,25 @@
     <t>2026-06-22</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Добрич Добруджа</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>B0264TE</t>
@@ -115,58 +133,115 @@
     <t>78970153027720803</t>
   </si>
   <si>
+    <t>1 Л. ЛЯTHA TEЧHOCT ЧИCTAЧKИ KOHЦEHTPAT</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>1 Л. ЛЯTHA TEЧHOCT ЧИCTAЧKИ KOHЦEHTPAT</t>
-  </si>
-  <si>
     <t>4 Л. ЛЯTHA TEЧHOCT ЗA ЧИCTAЧKИ ГOTOBA</t>
   </si>
   <si>
-    <t>2026-06-02 13:15:59</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:16:53</t>
-  </si>
-  <si>
-    <t>2026-06-04 14:27:32</t>
-  </si>
-  <si>
-    <t>2026-06-06 10:43:21</t>
-  </si>
-  <si>
-    <t>2026-06-08 08:35:04</t>
-  </si>
-  <si>
-    <t>2026-06-10 09:17:46</t>
-  </si>
-  <si>
-    <t>2026-06-10 16:59:06</t>
-  </si>
-  <si>
-    <t>2026-06-17 08:44:55</t>
-  </si>
-  <si>
-    <t>2026-06-17 08:44:56</t>
-  </si>
-  <si>
-    <t>2026-06-18 07:10:24</t>
-  </si>
-  <si>
-    <t>2026-06-18 08:12:38</t>
-  </si>
-  <si>
-    <t>2026-06-18 16:09:51</t>
-  </si>
-  <si>
-    <t>2026-06-22 08:58:15</t>
-  </si>
-  <si>
-    <t>2026-06-22 08:58:16</t>
-  </si>
-  <si>
-    <t>2026-06-22 18:38:30</t>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:16:00</t>
+  </si>
+  <si>
+    <t>13:15:00</t>
+  </si>
+  <si>
+    <t>14:27:00</t>
+  </si>
+  <si>
+    <t>10:42:00</t>
+  </si>
+  <si>
+    <t>08:34:00</t>
+  </si>
+  <si>
+    <t>09:17:00</t>
+  </si>
+  <si>
+    <t>16:59:00</t>
+  </si>
+  <si>
+    <t>08:44:00</t>
+  </si>
+  <si>
+    <t>08:12:00</t>
+  </si>
+  <si>
+    <t>16:10:00</t>
+  </si>
+  <si>
+    <t>07:10:00</t>
+  </si>
+  <si>
+    <t>08:58:00</t>
+  </si>
+  <si>
+    <t>18:38:00</t>
+  </si>
+  <si>
+    <t>10:15:00</t>
+  </si>
+  <si>
+    <t>14:08:00</t>
+  </si>
+  <si>
+    <t>09:01:00</t>
+  </si>
+  <si>
+    <t>3232733195 3232733195</t>
+  </si>
+  <si>
+    <t>3232734585 3232734585</t>
+  </si>
+  <si>
+    <t>3232855835 3232855835</t>
+  </si>
+  <si>
+    <t>3232952938 3232952938</t>
+  </si>
+  <si>
+    <t>3233034611 3233034611</t>
+  </si>
+  <si>
+    <t>3233140631 3233140631</t>
+  </si>
+  <si>
+    <t>3233151639 3233151639</t>
+  </si>
+  <si>
+    <t>3233475544 3233475544</t>
+  </si>
+  <si>
+    <t>3233502134 3233502134</t>
+  </si>
+  <si>
+    <t>3233530761 3233530761</t>
+  </si>
+  <si>
+    <t>3233514281 3233514281</t>
+  </si>
+  <si>
+    <t>3233690769 3233690769</t>
+  </si>
+  <si>
+    <t>3233720385 3233720385</t>
+  </si>
+  <si>
+    <t>3233918960 3233918960</t>
+  </si>
+  <si>
+    <t>3233939071 3233939071</t>
+  </si>
+  <si>
+    <t>3234088368 3234088368</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
@@ -584,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -593,14 +668,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -634,483 +712,609 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2">
+        <v>2.99</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="J2">
+        <v>2.99</v>
+      </c>
+      <c r="K2" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2">
+        <v>93484</v>
+      </c>
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3">
         <v>36.74</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3">
         <v>1.64</v>
       </c>
-      <c r="H2">
+      <c r="I3" s="1">
         <v>60.25</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J3">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K3" s="1">
         <v>62.09</v>
       </c>
-      <c r="K2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2.99</v>
-      </c>
-      <c r="H3">
-        <v>2.99</v>
-      </c>
-      <c r="I3" s="1">
-        <v>2.99</v>
-      </c>
-      <c r="J3">
-        <v>2.99</v>
-      </c>
-      <c r="K3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3">
+        <v>93484</v>
+      </c>
+      <c r="N3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>57.49</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4">
         <v>1.61</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>92.56</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.66</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>95.43000000000001</v>
       </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4">
+        <v>29576</v>
+      </c>
+      <c r="N4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>30.27</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5">
         <v>1.59</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>48.13</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.64</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>49.64</v>
       </c>
-      <c r="K5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5">
+        <v>29800</v>
+      </c>
+      <c r="N5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>75.91</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6">
         <v>1.59</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>120.7</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.64</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>124.49</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6">
+        <v>181698</v>
+      </c>
+      <c r="N6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
       </c>
       <c r="F7">
         <v>42.04</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7">
         <v>1.58</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>66.42</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.63</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>68.53</v>
       </c>
-      <c r="K7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7">
+        <v>15420</v>
+      </c>
+      <c r="N7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>42.25</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8">
         <v>1.58</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>66.76000000000001</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.63</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>68.87</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8">
+        <v>94317</v>
+      </c>
+      <c r="N8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>79.95999999999999</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9">
+        <v>1.54</v>
+      </c>
+      <c r="I9" s="1">
+        <v>123.14</v>
+      </c>
+      <c r="J9">
+        <v>1.59</v>
+      </c>
+      <c r="K9" s="1">
+        <v>127.14</v>
+      </c>
+      <c r="L9" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9">
+        <v>25018</v>
+      </c>
+      <c r="N9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="H10">
+        <v>9.49</v>
+      </c>
+      <c r="I10" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="J10">
+        <v>9.49</v>
+      </c>
+      <c r="K10" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10">
+        <v>25018</v>
+      </c>
+      <c r="N10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11">
+        <v>68.52</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11">
+        <v>1.53</v>
+      </c>
+      <c r="I11" s="1">
+        <v>104.84</v>
+      </c>
+      <c r="J11">
+        <v>1.58</v>
+      </c>
+      <c r="K11" s="1">
+        <v>108.26</v>
+      </c>
+      <c r="L11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11">
+        <v>30510</v>
+      </c>
+      <c r="N11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>81.2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12">
+        <v>1.53</v>
+      </c>
+      <c r="I12" s="1">
+        <v>124.24</v>
+      </c>
+      <c r="J12">
+        <v>1.58</v>
+      </c>
+      <c r="K12" s="1">
+        <v>128.3</v>
+      </c>
+      <c r="L12" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12">
+        <v>15920</v>
+      </c>
+      <c r="N12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13">
+        <v>37.41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13">
+        <v>1.53</v>
+      </c>
+      <c r="I13" s="1">
+        <v>57.24</v>
+      </c>
+      <c r="J13">
+        <v>1.58</v>
+      </c>
+      <c r="K13" s="1">
+        <v>59.11</v>
+      </c>
+      <c r="L13" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13">
+        <v>95041</v>
+      </c>
+      <c r="N13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
         <v>35</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1">
-        <v>9.49</v>
-      </c>
-      <c r="H9">
-        <v>9.49</v>
-      </c>
-      <c r="I9" s="1">
-        <v>9.49</v>
-      </c>
-      <c r="J9">
-        <v>9.49</v>
-      </c>
-      <c r="K9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10">
-        <v>79.95999999999999</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H10">
-        <v>123.14</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="J10">
-        <v>127.14</v>
-      </c>
-      <c r="K10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11">
-        <v>37.41</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H11">
-        <v>57.24</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J11">
-        <v>59.11</v>
-      </c>
-      <c r="K11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12">
-        <v>68.52</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H12">
-        <v>104.84</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J12">
-        <v>108.26</v>
-      </c>
-      <c r="K12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13">
-        <v>81.2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H13">
-        <v>124.24</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="J13">
-        <v>128.3</v>
-      </c>
-      <c r="K13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F14">
         <v>52.29</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14">
         <v>1.47</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>76.87</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>1.52</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>79.48</v>
       </c>
-      <c r="K14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14">
+        <v>31000</v>
+      </c>
+      <c r="N14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
-      <c r="G15" s="1">
-        <v>9.49</v>
+      <c r="G15" t="s">
+        <v>42</v>
       </c>
       <c r="H15">
         <v>9.49</v>
@@ -1121,156 +1325,306 @@
       <c r="J15">
         <v>9.49</v>
       </c>
-      <c r="K15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="K15" s="1">
+        <v>9.49</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15">
+        <v>31000</v>
+      </c>
+      <c r="N15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F16">
         <v>81.02</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16">
         <v>1.47</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>119.1</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.52</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>123.15</v>
       </c>
-      <c r="K16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="6">
-        <v>685.1</v>
-      </c>
-      <c r="C21" s="6">
-        <v>12</v>
-      </c>
-      <c r="D21" s="7">
-        <v>1.5476</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1060.25</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1094.49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="5" t="s">
+      <c r="L16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16">
+        <v>25864</v>
+      </c>
+      <c r="N16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="6">
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17">
+        <v>81.95999999999999</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17">
+        <v>1.46</v>
+      </c>
+      <c r="I17" s="1">
+        <v>119.66</v>
+      </c>
+      <c r="J17">
+        <v>1.51</v>
+      </c>
+      <c r="K17" s="1">
+        <v>123.76</v>
+      </c>
+      <c r="L17" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17">
+        <v>31760</v>
+      </c>
+      <c r="N17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18">
+        <v>46.47</v>
+      </c>
+      <c r="G18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18">
+        <v>1.46</v>
+      </c>
+      <c r="I18" s="1">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="J18">
+        <v>1.51</v>
+      </c>
+      <c r="K18" s="1">
+        <v>70.17</v>
+      </c>
+      <c r="L18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18">
+        <v>95809</v>
+      </c>
+      <c r="N18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>81.22</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19">
+        <v>1.46</v>
+      </c>
+      <c r="I19" s="1">
+        <v>118.58</v>
+      </c>
+      <c r="J19">
+        <v>1.51</v>
+      </c>
+      <c r="K19" s="1">
+        <v>122.64</v>
+      </c>
+      <c r="L19" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19">
+        <v>16800</v>
+      </c>
+      <c r="N19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="6">
+        <v>894.75</v>
+      </c>
+      <c r="C24" s="6">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.5271</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1366.34</v>
+      </c>
+      <c r="F24" s="6">
+        <v>1411.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C25" s="6">
         <v>2</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D25" s="7">
         <v>9.49</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E25" s="6">
         <v>18.98</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F25" s="6">
         <v>18.98</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="6">
+    <row r="26" spans="1:14">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6">
         <v>1</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C26" s="6">
         <v>1</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D26" s="7">
         <v>2.99</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E26" s="6">
         <v>2.99</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F26" s="6">
         <v>2.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="9">
-        <v>688.1</v>
-      </c>
-      <c r="C24" s="9">
-        <v>15</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="9">
-        <v>1082.22</v>
-      </c>
-      <c r="F24" s="9">
-        <v>1116.46</v>
+    <row r="27" spans="1:14">
+      <c r="A27" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="9">
+        <v>897.75</v>
+      </c>
+      <c r="C27" s="9">
+        <v>18</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="9">
+        <v>1388.31</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1433.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-07</t>
   </si>
   <si>
@@ -64,7 +70,22 @@
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>В8362ХЕ</t>
@@ -94,16 +115,61 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-07 08:40:28</t>
-  </si>
-  <si>
-    <t>2026-07-10 08:00:35</t>
-  </si>
-  <si>
-    <t>2026-07-11 08:16:54</t>
-  </si>
-  <si>
-    <t>2026-07-14 08:49:31</t>
+    <t>NOT 10LДOБABKA ADBLUE ДИЗEЛOBИ ДBИГATEЛИ</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>08:40:00</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>08:17:00</t>
+  </si>
+  <si>
+    <t>08:49:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>08:33:00</t>
+  </si>
+  <si>
+    <t>17:11:00</t>
+  </si>
+  <si>
+    <t>08:36:00</t>
+  </si>
+  <si>
+    <t>3234435434 3234435434</t>
+  </si>
+  <si>
+    <t>3234564359 3234564359</t>
+  </si>
+  <si>
+    <t>3234623497 3234623497</t>
+  </si>
+  <si>
+    <t>3234782548 3234782548</t>
+  </si>
+  <si>
+    <t>3235096611 3235096611</t>
+  </si>
+  <si>
+    <t>3235135459 3235135459</t>
+  </si>
+  <si>
+    <t>3235500235 3235500235</t>
+  </si>
+  <si>
+    <t>3235507046 3235507046</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
@@ -521,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,15 +596,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -575,230 +643,500 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>60.52</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2">
         <v>1.47</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>88.95999999999999</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>91.98999999999999</v>
       </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
         <v>14222</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>66.66</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3">
         <v>1.49</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>99.31999999999999</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.54</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>102.66</v>
       </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
         <v>32345</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>43.05</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4">
         <v>1.49</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>64.14</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>66.3</v>
       </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
         <v>96580</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>80.78</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5">
         <v>1.51</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>121.98</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.56</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>126.02</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>26610</v>
+      </c>
+      <c r="N5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6">
+        <v>83.95999999999999</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6">
+        <v>1.63</v>
+      </c>
+      <c r="I6" s="1">
+        <v>136.85</v>
+      </c>
+      <c r="J6">
+        <v>1.68</v>
+      </c>
+      <c r="K6" s="1">
+        <v>141.05</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>18420</v>
+      </c>
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
+        <v>23.79</v>
+      </c>
+      <c r="I7" s="1">
+        <v>23.79</v>
+      </c>
+      <c r="J7">
+        <v>23.79</v>
+      </c>
+      <c r="K7" s="1">
+        <v>23.79</v>
+      </c>
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>18420</v>
+      </c>
+      <c r="N7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8">
+        <v>40.35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8">
+        <v>1.63</v>
+      </c>
+      <c r="I8" s="1">
+        <v>65.77</v>
+      </c>
+      <c r="J8">
+        <v>1.68</v>
+      </c>
+      <c r="K8" s="1">
+        <v>67.79000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
+        <v>97374</v>
+      </c>
+      <c r="N8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9">
+        <v>43.59</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>1.69</v>
+      </c>
+      <c r="I9" s="1">
+        <v>73.67</v>
+      </c>
+      <c r="J9">
+        <v>1.74</v>
+      </c>
+      <c r="K9" s="1">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9">
+        <v>98232</v>
+      </c>
+      <c r="N9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="L5">
-        <v>26610</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="E10" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="F10">
+        <v>75.73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10">
+        <v>1.7</v>
+      </c>
+      <c r="I10" s="1">
+        <v>128.74</v>
+      </c>
+      <c r="J10">
+        <v>1.75</v>
+      </c>
+      <c r="K10" s="1">
+        <v>132.53</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10">
+        <v>33054</v>
+      </c>
+      <c r="N10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="6">
+        <v>494.64</v>
+      </c>
+      <c r="C15" s="6">
+        <v>8</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.5758</v>
+      </c>
+      <c r="E15" s="6">
+        <v>779.4299999999999</v>
+      </c>
+      <c r="F15" s="6">
+        <v>804.1900000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>23.79</v>
+      </c>
+      <c r="E16" s="6">
+        <v>23.79</v>
+      </c>
+      <c r="F16" s="6">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="9">
+        <v>495.64</v>
+      </c>
+      <c r="C17" s="9">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="6">
-        <v>251.01</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.4916</v>
-      </c>
-      <c r="E10" s="6">
-        <v>374.4</v>
-      </c>
-      <c r="F10" s="6">
-        <v>386.97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="9">
-        <v>251.01</v>
-      </c>
-      <c r="C11" s="9">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9">
-        <v>374.4</v>
-      </c>
-      <c r="F11" s="9">
-        <v>386.97</v>
+      <c r="D17" s="7"/>
+      <c r="E17" s="9">
+        <v>803.22</v>
+      </c>
+      <c r="F17" s="9">
+        <v>827.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -196,7 +196,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1087,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="7">
-        <v>1.5758</v>
+        <v>1.575752</v>
       </c>
       <c r="E15" s="6">
         <v>779.4299999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -587,7 +590,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -600,13 +603,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -649,248 +652,266 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>60.52</v>
       </c>
       <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>1.406</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="J2">
+        <v>88.9644</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L2" s="1">
+        <v>91.99039999999999</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2">
+        <v>14222</v>
+      </c>
+      <c r="O2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3">
+        <v>66.66200000000001</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>1.437</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J3">
+        <v>99.32638</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L3" s="1">
+        <v>102.65948</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3">
+        <v>32345</v>
+      </c>
+      <c r="O3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <v>43.052</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
+        <v>1.437</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J4">
+        <v>64.14748</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L4" s="1">
+        <v>66.30007999999999</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4">
+        <v>96580</v>
+      </c>
+      <c r="O4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5">
+        <v>80.782</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
+        <v>1.469</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J5">
+        <v>121.98082</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L5" s="1">
+        <v>126.01992</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5">
+        <v>26610</v>
+      </c>
+      <c r="O5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>83.958</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>1.546</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J6">
+        <v>136.85154</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L6" s="1">
+        <v>141.04944</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6">
+        <v>18420</v>
+      </c>
+      <c r="O6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
         <v>34</v>
-      </c>
-      <c r="H2">
-        <v>1.47</v>
-      </c>
-      <c r="I2" s="1">
-        <v>88.95999999999999</v>
-      </c>
-      <c r="J2">
-        <v>1.52</v>
-      </c>
-      <c r="K2" s="1">
-        <v>91.98999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2">
-        <v>14222</v>
-      </c>
-      <c r="N2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3">
-        <v>66.66</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3">
-        <v>1.49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>99.31999999999999</v>
-      </c>
-      <c r="J3">
-        <v>1.54</v>
-      </c>
-      <c r="K3" s="1">
-        <v>102.66</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3">
-        <v>32345</v>
-      </c>
-      <c r="N3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>43.05</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4">
-        <v>1.49</v>
-      </c>
-      <c r="I4" s="1">
-        <v>64.14</v>
-      </c>
-      <c r="J4">
-        <v>1.54</v>
-      </c>
-      <c r="K4" s="1">
-        <v>66.3</v>
-      </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4">
-        <v>96580</v>
-      </c>
-      <c r="N4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5">
-        <v>80.78</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5">
-        <v>1.51</v>
-      </c>
-      <c r="I5" s="1">
-        <v>121.98</v>
-      </c>
-      <c r="J5">
-        <v>1.56</v>
-      </c>
-      <c r="K5" s="1">
-        <v>126.02</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5">
-        <v>26610</v>
-      </c>
-      <c r="N5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6">
-        <v>83.95999999999999</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6">
-        <v>1.63</v>
-      </c>
-      <c r="I6" s="1">
-        <v>136.85</v>
-      </c>
-      <c r="J6">
-        <v>1.68</v>
-      </c>
-      <c r="K6" s="1">
-        <v>141.05</v>
-      </c>
-      <c r="L6" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6">
-        <v>18420</v>
-      </c>
-      <c r="N6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7">
         <v>23.79</v>
@@ -904,151 +925,163 @@
       <c r="K7" s="1">
         <v>23.79</v>
       </c>
-      <c r="L7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>23.79</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7">
         <v>18420</v>
       </c>
-      <c r="N7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>40.351</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
+        <v>1.564</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J8">
+        <v>65.77213</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L8" s="1">
+        <v>67.78968</v>
+      </c>
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+      <c r="N8">
+        <v>97374</v>
+      </c>
+      <c r="O8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9">
+        <v>43.592</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9">
+        <v>1.653</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J9">
+        <v>73.67048</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="L9" s="1">
+        <v>75.85008000000001</v>
+      </c>
+      <c r="M9" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9">
+        <v>98232</v>
+      </c>
+      <c r="O9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D10" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8">
-        <v>40.35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8">
-        <v>1.63</v>
-      </c>
-      <c r="I8" s="1">
-        <v>65.77</v>
-      </c>
-      <c r="J8">
-        <v>1.68</v>
-      </c>
-      <c r="K8" s="1">
-        <v>67.79000000000001</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8">
-        <v>97374</v>
-      </c>
-      <c r="N8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9">
-        <v>43.59</v>
-      </c>
-      <c r="G9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9">
-        <v>1.69</v>
-      </c>
-      <c r="I9" s="1">
-        <v>73.67</v>
-      </c>
-      <c r="J9">
-        <v>1.74</v>
-      </c>
-      <c r="K9" s="1">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="L9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9">
-        <v>98232</v>
-      </c>
-      <c r="N9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>75.73</v>
+        <v>75.73099999999999</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H10">
+        <v>1.674</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.7</v>
       </c>
-      <c r="I10" s="1">
-        <v>128.74</v>
-      </c>
       <c r="J10">
+        <v>128.7427</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.75</v>
       </c>
-      <c r="K10" s="1">
-        <v>132.53</v>
-      </c>
-      <c r="L10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>132.52925</v>
+      </c>
+      <c r="M10" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10">
         <v>33054</v>
       </c>
-      <c r="N10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1056,49 +1089,49 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6">
-        <v>494.64</v>
+        <v>494.648</v>
       </c>
       <c r="C15" s="6">
         <v>8</v>
       </c>
       <c r="D15" s="7">
-        <v>1.575752</v>
+        <v>1.575779</v>
       </c>
       <c r="E15" s="6">
-        <v>779.4299999999999</v>
+        <v>779.46</v>
       </c>
       <c r="F15" s="6">
         <v>804.1900000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="6">
         <v>1</v>
@@ -1118,17 +1151,17 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" s="9">
-        <v>495.64</v>
+        <v>495.648</v>
       </c>
       <c r="C17" s="9">
         <v>9</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="9">
-        <v>803.22</v>
+        <v>803.25</v>
       </c>
       <c r="F17" s="9">
         <v>827.98</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -198,8 +195,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -292,10 +289,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -603,13 +600,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -652,266 +649,248 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>60.52</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H2">
-        <v>1.406</v>
+        <v>1.47</v>
       </c>
       <c r="I2" s="1">
-        <v>1.47</v>
+        <v>88.964</v>
       </c>
       <c r="J2">
-        <v>88.9644</v>
+        <v>1.52</v>
       </c>
       <c r="K2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L2" s="1">
-        <v>91.99039999999999</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
         <v>14222</v>
       </c>
-      <c r="O2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>66.66200000000001</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H3">
-        <v>1.437</v>
+        <v>1.49</v>
       </c>
       <c r="I3" s="1">
-        <v>1.49</v>
+        <v>99.32599999999999</v>
       </c>
       <c r="J3">
-        <v>99.32638</v>
+        <v>1.54</v>
       </c>
       <c r="K3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L3" s="1">
-        <v>102.65948</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3">
+        <v>102.659</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
         <v>32345</v>
       </c>
-      <c r="O3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>43.052</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4">
-        <v>1.437</v>
+        <v>1.49</v>
       </c>
       <c r="I4" s="1">
-        <v>1.49</v>
+        <v>64.14700000000001</v>
       </c>
       <c r="J4">
-        <v>64.14748</v>
+        <v>1.54</v>
       </c>
       <c r="K4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L4" s="1">
-        <v>66.30007999999999</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4">
+        <v>66.3</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
         <v>96580</v>
       </c>
-      <c r="O4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
         <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
       </c>
       <c r="F5">
         <v>80.782</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5">
-        <v>1.469</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>121.981</v>
       </c>
       <c r="J5">
-        <v>121.98082</v>
+        <v>1.56</v>
       </c>
       <c r="K5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L5" s="1">
-        <v>126.01992</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5">
+        <v>126.02</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
         <v>26610</v>
       </c>
-      <c r="O5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>83.958</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H6">
-        <v>1.546</v>
+        <v>1.63</v>
       </c>
       <c r="I6" s="1">
-        <v>1.63</v>
+        <v>136.852</v>
       </c>
       <c r="J6">
-        <v>136.85154</v>
+        <v>1.68</v>
       </c>
       <c r="K6" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L6" s="1">
-        <v>141.04944</v>
-      </c>
-      <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6">
+        <v>141.049</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
         <v>18420</v>
       </c>
-      <c r="O6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7">
         <v>23.79</v>
@@ -925,163 +904,151 @@
       <c r="K7" s="1">
         <v>23.79</v>
       </c>
-      <c r="L7" s="1">
-        <v>23.79</v>
-      </c>
-      <c r="M7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7">
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7">
         <v>18420</v>
       </c>
-      <c r="O7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>40.351</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8">
-        <v>1.564</v>
+        <v>1.63</v>
       </c>
       <c r="I8" s="1">
-        <v>1.63</v>
+        <v>65.77200000000001</v>
       </c>
       <c r="J8">
-        <v>65.77213</v>
+        <v>1.68</v>
       </c>
       <c r="K8" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L8" s="1">
-        <v>67.78968</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8">
+        <v>67.79000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
         <v>97374</v>
       </c>
-      <c r="O8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>43.592</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>1.653</v>
+        <v>1.69</v>
       </c>
       <c r="I9" s="1">
-        <v>1.69</v>
+        <v>73.67</v>
       </c>
       <c r="J9">
-        <v>73.67048</v>
+        <v>1.74</v>
       </c>
       <c r="K9" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L9" s="1">
-        <v>75.85008000000001</v>
-      </c>
-      <c r="M9" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9">
         <v>98232</v>
       </c>
-      <c r="O9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>75.73099999999999</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H10">
-        <v>1.674</v>
+        <v>1.7</v>
       </c>
       <c r="I10" s="1">
-        <v>1.7</v>
+        <v>128.743</v>
       </c>
       <c r="J10">
-        <v>128.7427</v>
+        <v>1.75</v>
       </c>
       <c r="K10" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L10" s="1">
-        <v>132.52925</v>
-      </c>
-      <c r="M10" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10">
+        <v>132.529</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10">
         <v>33054</v>
       </c>
-      <c r="O10" t="s">
+      <c r="N10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="3" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="A13" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1089,69 +1056,69 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" s="6">
         <v>494.648</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>8</v>
       </c>
       <c r="D15" s="7">
-        <v>1.575779</v>
-      </c>
-      <c r="E15" s="6">
-        <v>779.46</v>
-      </c>
-      <c r="F15" s="6">
-        <v>804.1900000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>1.576</v>
+      </c>
+      <c r="E15" s="7">
+        <v>779.455</v>
+      </c>
+      <c r="F15" s="7">
+        <v>804.187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="6">
         <v>1</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>1</v>
       </c>
       <c r="D16" s="7">
         <v>23.79</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>23.79</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>23.79</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B17" s="9">
         <v>495.648</v>
@@ -1161,10 +1128,10 @@
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="9">
-        <v>803.25</v>
+        <v>803.245</v>
       </c>
       <c r="F17" s="9">
-        <v>827.98</v>
+        <v>827.977</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДИМИТРОВ ЕКСПРЕС КАРГО ООД/ДИМИТРОВ ЕКСПРЕС КАРГО ООД.xlsx
@@ -706,10 +706,10 @@
         <v>38</v>
       </c>
       <c r="H2" s="1">
-        <v>1.657</v>
+        <v>1.75</v>
       </c>
       <c r="I2" s="1">
-        <v>102.403</v>
+        <v>108.15</v>
       </c>
       <c r="J2" s="1">
         <v>1.8</v>
@@ -794,10 +794,10 @@
         <v>38</v>
       </c>
       <c r="H4" s="1">
-        <v>1.657</v>
+        <v>1.75</v>
       </c>
       <c r="I4" s="1">
-        <v>64.822</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="J4" s="1">
         <v>1.8</v>
@@ -838,10 +838,10 @@
         <v>38</v>
       </c>
       <c r="H5" s="1">
-        <v>1.657</v>
+        <v>1.75</v>
       </c>
       <c r="I5" s="1">
-        <v>112.179</v>
+        <v>118.475</v>
       </c>
       <c r="J5" s="1">
         <v>1.8</v>
@@ -882,10 +882,10 @@
         <v>38</v>
       </c>
       <c r="H6" s="1">
-        <v>1.657</v>
+        <v>1.75</v>
       </c>
       <c r="I6" s="1">
-        <v>120.911</v>
+        <v>127.697</v>
       </c>
       <c r="J6" s="1">
         <v>1.8</v>
@@ -926,10 +926,10 @@
         <v>38</v>
       </c>
       <c r="H7" s="1">
-        <v>1.624</v>
+        <v>1.75</v>
       </c>
       <c r="I7" s="1">
-        <v>124.804</v>
+        <v>134.487</v>
       </c>
       <c r="J7" s="1">
         <v>1.8</v>
@@ -970,10 +970,10 @@
         <v>38</v>
       </c>
       <c r="H8" s="1">
-        <v>1.624</v>
+        <v>1.74</v>
       </c>
       <c r="I8" s="1">
-        <v>65.447</v>
+        <v>70.122</v>
       </c>
       <c r="J8" s="1">
         <v>1.79</v>
@@ -1014,10 +1014,10 @@
         <v>38</v>
       </c>
       <c r="H9" s="1">
-        <v>1.657</v>
+        <v>1.77</v>
       </c>
       <c r="I9" s="1">
-        <v>116.653</v>
+        <v>124.608</v>
       </c>
       <c r="J9" s="1">
         <v>1.82</v>
@@ -1102,10 +1102,10 @@
         <v>38</v>
       </c>
       <c r="H11" s="1">
-        <v>1.669</v>
+        <v>1.78</v>
       </c>
       <c r="I11" s="1">
-        <v>62.638</v>
+        <v>66.803</v>
       </c>
       <c r="J11" s="1">
         <v>1.83</v>
@@ -1146,10 +1146,10 @@
         <v>38</v>
       </c>
       <c r="H12" s="1">
-        <v>1.699</v>
+        <v>1.8</v>
       </c>
       <c r="I12" s="1">
-        <v>110.877</v>
+        <v>117.468</v>
       </c>
       <c r="J12" s="1">
         <v>1.85</v>
@@ -1190,10 +1190,10 @@
         <v>38</v>
       </c>
       <c r="H13" s="1">
-        <v>1.699</v>
+        <v>1.8</v>
       </c>
       <c r="I13" s="1">
-        <v>63.746</v>
+        <v>67.536</v>
       </c>
       <c r="J13" s="1">
         <v>1.85</v>
@@ -1234,10 +1234,10 @@
         <v>38</v>
       </c>
       <c r="H14" s="1">
-        <v>1.699</v>
+        <v>1.8</v>
       </c>
       <c r="I14" s="1">
-        <v>138.876</v>
+        <v>147.132</v>
       </c>
       <c r="J14" s="1">
         <v>1.85</v>
@@ -1296,10 +1296,10 @@
         <v>11</v>
       </c>
       <c r="D19" s="8">
-        <v>1.66366</v>
+        <v>1.76744</v>
       </c>
       <c r="E19" s="6">
-        <v>1083.36</v>
+        <v>1150.94</v>
       </c>
       <c r="F19" s="6">
         <v>1183.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="10">
-        <v>1102.34</v>
+        <v>1169.92</v>
       </c>
       <c r="F21" s="10">
         <v>1202.48</v>
